--- a/shvilim/classform/names.xlsx
+++ b/shvilim/classform/names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shvilim\14 אפליקציות\Svilim\ערבוב כיתות\class-form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E088D03E-BD16-46EB-A9AC-D22537EFDA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E53352-5E69-4618-AC4E-2691972BDAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6958F6-7426-41DC-A55E-66E011C41F81}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>הראל איתמר</t>
   </si>
@@ -99,18 +99,147 @@
   </si>
   <si>
     <t>בן צבי יונתן גבע</t>
+  </si>
+  <si>
+    <t>אל- אור אביגיל</t>
+  </si>
+  <si>
+    <t>אלטרמן יהונתן</t>
+  </si>
+  <si>
+    <t>אלמוג עדן</t>
+  </si>
+  <si>
+    <t>אפק גאיה</t>
+  </si>
+  <si>
+    <t>ארבל סלע עינב</t>
+  </si>
+  <si>
+    <t>בן צבי שדה קדם</t>
+  </si>
+  <si>
+    <t>ברק גלי ניקי</t>
+  </si>
+  <si>
+    <t>דוכין אילה</t>
+  </si>
+  <si>
+    <t>הירשברג ג'וי</t>
+  </si>
+  <si>
+    <t>וולדנר אלי ציפורה</t>
+  </si>
+  <si>
+    <t>וסילי נועם שמואל</t>
+  </si>
+  <si>
+    <t>טולידנו איתן צבר</t>
+  </si>
+  <si>
+    <t>לסרי נור</t>
+  </si>
+  <si>
+    <t>רענן אורי</t>
+  </si>
+  <si>
+    <t>שמש בר</t>
+  </si>
+  <si>
+    <t>שמש חכימזדה ים</t>
+  </si>
+  <si>
+    <t>דיאמנט שיר רוז</t>
+  </si>
+  <si>
+    <t>טוק ימה</t>
+  </si>
+  <si>
+    <t>לוי אייזנר טליה</t>
+  </si>
+  <si>
+    <t>נוף דרור</t>
+  </si>
+  <si>
+    <t>עמרם גפן</t>
+  </si>
+  <si>
+    <t>שבתאי שקד</t>
+  </si>
+  <si>
+    <t>שור מעיין</t>
+  </si>
+  <si>
+    <t>שילה שביב שובל</t>
+  </si>
+  <si>
+    <t>שלומיאן טליה</t>
+  </si>
+  <si>
+    <t>בן צור אריאה</t>
+  </si>
+  <si>
+    <t>בר עוז עמליה</t>
+  </si>
+  <si>
+    <t>דקר דורון</t>
+  </si>
+  <si>
+    <t>וולנדר תום אפרים</t>
+  </si>
+  <si>
+    <t>וידס רובי</t>
+  </si>
+  <si>
+    <t>וקסלר ניתאי</t>
+  </si>
+  <si>
+    <t>יפה חממי אלי</t>
+  </si>
+  <si>
+    <t>לביא רפאלי</t>
+  </si>
+  <si>
+    <t>גילי נחמיאס</t>
+  </si>
+  <si>
+    <t>עדני אסיה</t>
+  </si>
+  <si>
+    <t>קופר ארבל</t>
+  </si>
+  <si>
+    <t>קורט מיקה</t>
+  </si>
+  <si>
+    <t>רשף מיילי שחר</t>
+  </si>
+  <si>
+    <t>שגב מיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">דיאמנט אלה מרגו </t>
+  </si>
+  <si>
+    <t>שפר טמיר שחר</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -134,8 +263,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,107 +600,315 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58DDF56D-F263-49B8-9D47-6630BC923127}">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
